--- a/prix/sikkens.xlsx
+++ b/prix/sikkens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39FD94C-1A15-465E-A9BB-8DB38531A783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C369D97-8892-440B-9C76-5008CAFBFD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -922,7 +922,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="11">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1282,7 +1282,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1402,7 +1402,7 @@
         <v>30</v>
       </c>
       <c r="F26" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1422,7 +1422,7 @@
         <v>31</v>
       </c>
       <c r="F27" s="11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1572,13 +1572,13 @@
         <v>99</v>
       </c>
       <c r="D35" s="10">
-        <v>64.5</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F35" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1598,7 +1598,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="F37" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1798,7 +1798,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
